--- a/output/xlsx/AdministradorRegistraOcorrenciaEmNota--GT-.xlsx
+++ b/output/xlsx/AdministradorRegistraOcorrenciaEmNota--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="72">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 13 test case(s)</t>
+    <t>Size: 12 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -101,25 +101,25 @@
     <t>SYSTEM exibe Dashboard do sistema</t>
   </si>
   <si>
-    <t>Administrador: clica em contador 'Outros'</t>
-  </si>
-  <si>
-    <t>SYSTEM abre uma tela com a lista de 'Pedidos' ou Notas</t>
-  </si>
-  <si>
-    <t>Administrador: seleciona algum Pedido ou Nota da lista</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe os dados da Nota</t>
+    <t>Administrador: clica em tab 'Pedidos'</t>
+  </si>
+  <si>
+    <t>SYSTEM abre uma tela com a lista de 'Pedidos'</t>
+  </si>
+  <si>
+    <t>Administrador: seleciona algum Pedido (NFe) da lista</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe os dados da nota</t>
   </si>
   <si>
     <t>Administrador: clica no botao de 'Registrar Ocorrencia'</t>
   </si>
   <si>
-    <t>SYSTEM abre modal para digitacao da Ocorrencia</t>
-  </si>
-  <si>
-    <t>Administrador: digita Ocorrencia e clica em 'Confirmar'</t>
+    <t>SYSTEM abre modal para digitacao da ocorrencia</t>
+  </si>
+  <si>
+    <t>Administrador: digita ocorrencia e clica em 'Confirmar'</t>
   </si>
   <si>
     <t>SYSTEM notifica que Ocorrencia foi registrada com sucesso</t>
@@ -215,28 +215,19 @@
     <t>TC11</t>
   </si>
   <si>
-    <t>Alternative Flow 10: Filtra notas da lista</t>
-  </si>
-  <si>
-    <t>Administrador: filtra as notas por algum campo</t>
+    <t>Alternative Flow 10: Filtra pedidos da lista</t>
+  </si>
+  <si>
+    <t>Administrador: filtra os pedidos por algum campo</t>
   </si>
   <si>
     <t>TC12</t>
   </si>
   <si>
-    <t>Alternative Flow 11: Volta para lista de notas</t>
-  </si>
-  <si>
-    <t>Administrador: clica em botão 'Voltar'</t>
-  </si>
-  <si>
-    <t>TC13</t>
-  </si>
-  <si>
-    <t>Alternative Flow 12: Seleciona contador de 'Ocorrencias'</t>
-  </si>
-  <si>
-    <t>Administrador: clica em algum contador de 'Ocorrencias' na secao de 'Notas'</t>
+    <t>Alternative Flow 11: Volta para lista de pedidos</t>
+  </si>
+  <si>
+    <t>Administrador: clica em botão Voltar</t>
   </si>
 </sst>
 </file>
@@ -328,7 +319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -2490,167 +2481,6 @@
         <v>38</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B159" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="C159" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E159" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="E160" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B161" t="s" s="0">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D162" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E162" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F162" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B163" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C163" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D163" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E163" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F163" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B164" t="s" s="3">
-        <v>74</v>
-      </c>
-      <c r="C164" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D164" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E164" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F164" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B165" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C165" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D165" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E165" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F165" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B166" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C166" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D166" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E166" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F166" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B167" t="s" s="3">
-        <v>35</v>
-      </c>
-      <c r="C167" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D167" t="s" s="3">
-        <v>36</v>
-      </c>
-      <c r="E167" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F167" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="1">
-        <v>37</v>
-      </c>
-      <c r="B168" t="s" s="0">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
